--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -637,24 +637,24 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站德川路华夏东路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -756,24 +756,24 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站博兴路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -875,29 +875,29 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站德川路华夏东路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -994,29 +994,29 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1118,26 +1118,22 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 41分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1145,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1174,7 +1170,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1184,22 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1245,12 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
+          <t>07:21采样：该车到重点站唐陆公路唐镇路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1264,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1293,7 +1289,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1318,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -1356,22 +1352,26 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>07:21采样：该车到重点站唐陆公路创新路 ETA 37分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1423,13 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1467,24 +1471,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±8分钟</t>
+          <t>07:21采样：该车到重点站唐陆公路唐镇路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1518,12 +1522,12 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1543,12 +1547,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1556,24 +1560,24 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -1586,34 +1590,34 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±8分钟</t>
+          <t>07:21采样：该车到重点站新德西路德翔路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1627,47 +1631,880 @@
       <c r="T10" s="2" t="inlineStr"/>
       <c r="U10" s="2" t="inlineStr">
         <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>07:21采样：该车到重点站东陆路金海路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W10" s="2" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X10" s="2" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y10" s="2" t="inlineStr">
+      <c r="Y12" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z10" s="2" t="inlineStr">
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
+      <c r="AA12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
+      <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>87.0</t>
         </is>
       </c>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>7/9</t>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>7/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>12/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1113,27 +1113,31 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 41分钟</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1141,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1165,12 +1169,12 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1195,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1228,29 +1232,29 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站唐陆公路唐镇路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1260,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1284,12 +1288,12 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1299,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1347,24 +1351,24 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站唐陆公路创新路 ETA 37分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1379,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1403,12 +1407,12 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1418,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1466,29 +1470,29 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站唐陆公路唐镇路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1498,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1522,12 +1526,12 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1537,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1585,29 +1589,29 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站新德西路德翔路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1617,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,12 +1645,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1656,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1704,29 +1708,29 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站东陆路金海路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1736,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1760,12 +1764,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1775,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1828,26 +1832,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:22采样，终点ETA 38分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±9分钟</t>
+          <t>08:22采样：该车到重点站唐陆公路川桥路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2066,24 +2066,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±14分钟</t>
+          <t>08:22采样：该车到重点站唐陆公路川桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2185,24 +2185,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±12分钟</t>
+          <t>08:12采样：该车到重点站新德西路德川路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2236,12 +2236,12 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2304,24 +2304,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±6分钟</t>
+          <t>08:22采样：该车到重点站唐陆公路川桥路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2393,24 +2393,24 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2423,24 +2423,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±9分钟</t>
+          <t>08:22采样：该车到重点站德川路华夏东路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2464,47 +2464,999 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>08:22采样：该车到重点站新川路华东路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>08:22采样：该车到重点站博兴路东陆路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="Y20" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>83.5</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>9/13</t>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1594,24 +1594,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1713,24 +1713,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1837,17 +1837,21 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:22采样，终点ETA 38分钟</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1855,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1879,12 +1883,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1894,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1946,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1959,12 +1963,12 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站唐陆公路川桥路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1974,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1998,12 +2002,12 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -2013,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2066,24 +2070,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站唐陆公路川桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±6分钟</t>
+          <t>08:43采样：该车到重点站佳林路金高路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数22分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2185,24 +2189,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:12采样：该车到重点站新德西路德川路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±6分钟</t>
+          <t>08:43采样：该车到重点站唐陆公路锦绣东路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2212,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2261,7 +2265,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2304,7 +2308,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2316,12 +2320,12 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站唐陆公路川桥路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+          <t>08:43采样：该车到重点站唐陆公路春雅路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2331,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2385,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2427,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2435,12 +2439,12 @@
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站德川路华夏东路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
+          <t>08:43采样：该车到重点站唐陆公路锦绣东路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2450,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2504,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2542,19 +2546,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站新川路华东路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
+          <t>08:43采样：该车到重点站唐陆公路唐镇路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2569,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2618,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2665,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2673,12 +2677,12 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站博兴路东陆路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±11分钟</t>
+          <t>08:43采样：该车到重点站唐陆公路春雅路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2688,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,7 +2716,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
@@ -2742,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2780,19 +2784,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+          <t>08:43采样：该车到重点站唐陆公路唐镇路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2807,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2836,7 +2840,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2856,12 +2860,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2899,19 +2903,19 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+          <t>08:43采样：该车到重点站东陆路金海路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2926,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,7 +2959,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2975,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3164,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3218,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3332,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3451,12 +3455,250 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
           <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1832,24 +1832,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1951,24 +1951,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2065,29 +2065,29 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:43采样：该车到重点站佳林路金高路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数22分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2184,29 +2184,29 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:43采样：该车到重点站唐陆公路锦绣东路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2303,29 +2303,29 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:43采样：该车到重点站唐陆公路春雅路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2427,26 +2427,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>08:43采样：该车到重点站唐陆公路锦绣东路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:14采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2454,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2483,7 +2479,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2503,12 +2499,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2546,19 +2542,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:43采样：该车到重点站唐陆公路唐镇路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
+          <t>09:03采样：该车到重点站唐陆公路川桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2573,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2618,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2665,26 +2661,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:43采样：该车到重点站唐陆公路春雅路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:14采样，终点ETA 27分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2692,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,12 +2708,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2731,22 +2723,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2784,24 +2776,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>08:43采样：该车到重点站唐陆公路唐镇路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±14分钟</t>
+          <t>09:03采样：该车到重点站唐陆公路龙东大道 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2811,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,7 +2827,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -2860,12 +2852,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2903,24 +2895,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>08:43采样：该车到重点站东陆路金海路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±8分钟</t>
+          <t>09:14采样：该车到重点站唐陆公路锦绣东路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2930,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2971,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3022,24 +3014,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±12分钟</t>
+          <t>09:03采样：该车到重点站新川路华东路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3049,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3078,7 +3070,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3098,12 +3090,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3260,24 +3252,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
+          <t>09:14采样：该车到重点站唐陆公路创新路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3287,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3311,12 +3303,12 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3336,12 +3328,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3525,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,7 +3566,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,12 +3685,484 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
           <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>70分钟</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2308,24 +2308,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2422,27 +2422,31 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:14采样，终点ETA 19分钟</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2450,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2474,12 +2478,12 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2489,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2537,29 +2541,29 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>09:03采样：该车到重点站唐陆公路川桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2569,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2593,12 +2597,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2608,17 +2612,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2656,7 +2660,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2666,17 +2670,21 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:14采样，终点ETA 27分钟</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2684,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2708,12 +2716,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2733,12 +2741,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2771,29 +2779,29 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>09:03采样：该车到重点站唐陆公路龙东大道 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2803,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2827,12 +2835,12 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2842,22 +2850,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2890,29 +2898,29 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>09:14采样：该车到重点站唐陆公路锦绣东路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2922,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2946,12 +2954,12 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2961,17 +2969,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3009,29 +3017,29 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>09:03采样：该车到重点站新川路华东路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±11分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3041,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3065,12 +3073,12 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3080,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3128,29 +3136,29 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3160,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3184,12 +3192,12 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3209,12 +3217,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3247,29 +3255,29 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>09:14采样：该车到重点站唐陆公路创新路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3279,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3303,12 +3311,12 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3318,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3366,29 +3374,29 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3398,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3422,12 +3430,12 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3437,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3490,26 +3498,22 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:12采样，终点ETA 25分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3517,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3541,12 +3545,12 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3566,12 +3570,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3609,24 +3613,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±8分钟</t>
+          <t>10:22采样：该车到重点站博兴路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数13分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3636,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3665,7 +3669,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3685,7 +3689,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3728,24 +3732,24 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+          <t>10:22采样：该车到重点站德川路华夏东路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3755,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3784,7 +3788,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3794,22 +3798,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3847,22 +3851,26 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>10:22采样：该车到重点站唐陆公路龙东大道 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -3870,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3894,17 +3902,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3914,17 +3922,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3962,19 +3970,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
+          <t>10:22采样：该车到重点站唐陆公路龙东大道 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3989,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4018,7 +4026,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4038,12 +4046,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4051,24 +4059,24 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4081,24 +4089,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±14分钟</t>
+          <t>10:22采样：该车到重点站博兴路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4108,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4122,47 +4130,999 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>10:22采样：该车到重点站新川路华东路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>10:22采样：该车到重点站博兴路东陆路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
+      <c r="X38" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y31" s="2" t="inlineStr">
+      <c r="Y38" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>83.0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>4/14</t>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3510,10 +3510,14 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:12采样，终点ETA 25分钟</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3521,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,12 +3549,12 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3613,26 +3617,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10:22采样：该车到重点站博兴路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数13分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:32采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3679,22 +3679,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3732,26 +3732,22 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10:22采样：该车到重点站德川路华夏东路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:32采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3759,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3788,7 +3784,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3808,12 +3804,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3851,26 +3847,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10:22采样：该车到重点站唐陆公路龙东大道 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±13分钟</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:51采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -3878,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3902,12 +3894,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3917,22 +3909,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3965,29 +3957,29 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10:22采样：该车到重点站唐陆公路龙东大道 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3997,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4021,12 +4013,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4036,22 +4028,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4084,29 +4076,29 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10:22采样：该车到重点站博兴路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4116,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4140,12 +4132,12 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4165,12 +4157,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4203,24 +4195,24 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10:22采样：该车到重点站新川路华东路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -4235,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4259,12 +4251,12 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4274,22 +4266,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4322,29 +4314,29 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10:22采样：该车到重点站博兴路东陆路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4354,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4378,12 +4370,12 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4403,12 +4395,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4446,26 +4438,22 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：11:21采样，终点ETA 24分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -4473,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4497,12 +4485,12 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4512,17 +4500,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4560,29 +4548,29 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4592,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4616,12 +4604,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4631,22 +4619,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4684,24 +4672,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±7分钟</t>
+          <t>11:21采样：该车到重点站唐陆公路春雅路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4711,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4740,7 +4728,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4760,12 +4748,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4815,12 +4803,12 @@
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±8分钟</t>
+          <t>11:21采样：该车到重点站东陆路金海路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4830,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4859,7 +4847,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4884,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4922,24 +4910,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±12分钟</t>
+          <t>11:21采样：该车到重点站新德西路德翔路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4949,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4973,12 +4961,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4998,12 +4986,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5011,24 +4999,24 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5041,7 +5029,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -5053,22 +5041,22 @@
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+          <t>11:21采样：该车到重点站长岛路台儿庄路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5082,47 +5070,761 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>82.3</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>12/14</t>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>70分钟</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>67分钟</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数67分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>69分钟</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数69分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,22 +3794,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,22 +3909,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,22 +4385,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4433,27 +4433,31 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：11:21采样，终点ETA 24分钟</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -4461,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4485,12 +4489,12 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4510,7 +4514,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4580,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4629,7 +4633,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4672,26 +4676,22 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站唐陆公路春雅路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:02采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4786,29 +4786,29 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站东陆路金海路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4905,29 +4905,29 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站新德西路德翔路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5024,29 +5024,29 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站长岛路台儿庄路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5143,29 +5143,29 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>65分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5214,22 +5214,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5267,26 +5267,22 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 25分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5294,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5318,12 +5314,12 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5343,7 +5339,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5386,26 +5382,22 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 44分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5413,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5437,12 +5429,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5452,22 +5444,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5505,19 +5497,19 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±5分钟</t>
+          <t>12:21采样：该车到重点站唐陆公路川桥路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -5532,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5561,7 +5553,7 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5581,7 +5573,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5624,24 +5616,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>67分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数67分钟估算，约±7分钟</t>
+          <t>12:21采样：该车到重点站德川路华夏东路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5651,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5680,7 +5672,7 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5700,7 +5692,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5748,19 +5740,19 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数69分钟估算，约±12分钟</t>
+          <t>12:21采样：该车到重点站金杨路金桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5770,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5794,37 +5786,747 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y45" s="2" t="inlineStr">
+      <c r="Y46" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr">
-        <is>
-          <t>2/14</t>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,17 +4504,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,17 +4738,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,22 +4857,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5029,24 +5029,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5148,12 +5148,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>65分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5262,12 +5262,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -5279,10 +5279,14 @@
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 25分钟</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5290,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5314,12 +5318,12 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5344,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5377,27 +5381,31 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 44分钟</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5405,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5429,12 +5437,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5454,12 +5462,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5500,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5509,12 +5517,12 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站唐陆公路川桥路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5524,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5548,12 +5556,12 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5578,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5611,29 +5619,29 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站德川路华夏东路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5643,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5667,12 +5675,12 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5682,17 +5690,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5730,29 +5738,29 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站金杨路金桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5762,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5786,12 +5794,12 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5811,12 +5819,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5854,7 +5862,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5866,14 +5874,10 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:21采样，终点ETA 33分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5881,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5905,12 +5909,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5935,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5968,29 +5972,29 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6000,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6024,12 +6028,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6039,22 +6043,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6092,24 +6096,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+          <t>13:21采样：该车到重点站东陆路金海路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6119,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6148,7 +6152,7 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6168,7 +6172,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6211,24 +6215,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±6分钟</t>
+          <t>13:21采样：该车到重点站新德西路德翔路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6238,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6267,7 +6271,7 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6287,7 +6291,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6353,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6402,12 +6406,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6526,6 +6530,482 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
           <t>9/14</t>
         </is>
       </c>

--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,22 +3679,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3914,17 +3914,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,22 +4385,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,22 +5095,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5457,17 +5457,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5867,17 +5867,21 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:21采样，终点ETA 33分钟</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5885,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5909,12 +5913,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5934,7 +5938,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5977,12 +5981,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -6004,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6053,12 +6057,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6091,29 +6095,29 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站东陆路金海路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6123,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6147,12 +6151,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6172,12 +6176,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6210,29 +6214,29 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站新德西路德翔路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6242,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6266,12 +6270,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6281,22 +6285,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6334,19 +6338,19 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：14:02采样，终点ETA 35分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
@@ -6357,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6381,17 +6385,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6401,17 +6405,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6449,26 +6453,22 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:02采样，终点ETA 45分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6500,12 +6500,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6515,22 +6515,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6568,24 +6568,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±8分钟</t>
+          <t>14:02采样：该车到重点站东陆路金海路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6687,24 +6687,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±9分钟</t>
+          <t>14:02采样：该车到重点站新德西路德翔路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6882,12 +6882,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7006,6 +7006,363 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>70分钟</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
           <t>9/14</t>
         </is>
       </c>

--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,22 +3207,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6219,12 +6219,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>67分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -6350,10 +6350,14 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:02采样，终点ETA 35分钟</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6361,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6385,12 +6389,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6448,7 +6452,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -6465,10 +6469,14 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:02采样，终点ETA 45分钟</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6476,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6500,12 +6508,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6530,7 +6538,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6563,29 +6571,29 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>14:02采样：该车到重点站东陆路金海路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6595,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6619,12 +6627,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6644,7 +6652,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6687,26 +6695,22 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>14:02采样：该车到重点站新德西路德翔路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:22采样，终点ETA 50分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6714,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6738,22 +6742,22 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6763,7 +6767,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6806,24 +6810,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±7分钟</t>
+          <t>14:22采样：该车到重点站博兴路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6833,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6862,7 +6866,7 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6882,12 +6886,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6925,24 +6929,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+          <t>14:22采样：该车到重点站新川路华东路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6952,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6981,7 +6985,7 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -7001,7 +7005,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7071,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7120,7 +7124,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7190,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7244,7 +7248,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7252,24 +7256,24 @@
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>沪A13735A</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7282,19 +7286,19 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -7304,12 +7308,12 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7348,22 +7352,260 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>77.8</t>
         </is>
       </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>9/14</t>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,22 +3207,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,12 +3679,12 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,22 +4028,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,22 +4266,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,22 +4623,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,22 +4857,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5333,22 +5333,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5571,22 +5571,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5809,22 +5809,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,22 +5928,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6576,24 +6576,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>65分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6690,27 +6690,31 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:22采样，终点ETA 50分钟</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6718,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6742,17 +6746,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6762,12 +6766,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6805,7 +6809,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -6822,12 +6826,12 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>14:22采样：该车到重点站博兴路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±10分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6837,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6861,12 +6865,12 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6924,29 +6928,29 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>14:22采样：该车到重点站新川路华东路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6956,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6980,12 +6984,12 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -6995,22 +6999,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7043,29 +7047,29 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7075,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7099,12 +7103,12 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7124,12 +7128,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7162,29 +7166,29 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±14分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7194,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7218,12 +7222,12 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7233,12 +7237,12 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
@@ -7286,24 +7290,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>63分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±5分钟</t>
+          <t>同车下一次反向发车16:20，减去该车自身同类时段历史终点停站中位数17分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7313,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7342,7 +7346,7 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7352,22 +7356,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7405,19 +7409,19 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+          <t>15:22采样：该车到重点站东陆路金海路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7432,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7461,7 +7465,7 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7481,12 +7485,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7494,24 +7498,24 @@
       <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7524,24 +7528,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±7分钟</t>
+          <t>15:22采样：该车到重点站新川路妙境路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7551,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7565,47 +7569,880 @@
       <c r="T60" s="2" t="inlineStr"/>
       <c r="U60" s="2" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>73.6</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="V60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>15:22采样：该车到重点站长岛路台儿庄路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W60" s="2" t="inlineStr">
+      <c r="W61" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X60" s="2" t="inlineStr">
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>79.8</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>70分钟</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y60" s="2" t="inlineStr">
+      <c r="Y62" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA60" s="2" t="inlineStr">
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>74.4</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>78.4</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>78.4</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>81.2</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>14/14</t>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>72.8</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,12 +2493,12 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,22 +3794,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,22 +3909,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,22 +4028,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,22 +4266,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,22 +4623,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,22 +5214,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5333,22 +5333,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,22 +5452,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5571,22 +5571,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5809,22 +5809,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6047,22 +6047,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6166,22 +6166,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6404,22 +6404,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6880,22 +6880,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6933,24 +6933,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7171,24 +7171,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7285,29 +7285,29 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>63分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车16:20，减去该车自身同类时段历史终点停站中位数17分钟，约±8分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7341,12 +7341,12 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7404,24 +7404,24 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>15:22采样：该车到重点站东陆路金海路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7485,12 +7485,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7523,29 +7523,29 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>67分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>15:22采样：该车到重点站新川路妙境路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7594,22 +7594,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7642,29 +7642,29 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>15:22采样：该车到重点站长岛路台儿庄路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7766,26 +7766,22 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:22采样，终点ETA 17分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -7793,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7822,7 +7818,7 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7832,22 +7828,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7885,19 +7881,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+          <t>16:22采样：该车到重点站唐陆公路龙东大道 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -7912,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7941,7 +7937,7 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7961,12 +7957,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8004,24 +8000,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±14分钟</t>
+          <t>16:22采样：该车到重点站唐陆公路川桥路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8031,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8055,12 +8051,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8070,22 +8066,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8131,12 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±12分钟</t>
+          <t>16:22采样：该车到重点站德川路华夏东路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8150,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8179,7 +8175,7 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8204,7 +8200,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8242,24 +8238,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
+          <t>16:22采样：该车到重点站唐陆公路川桥路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8269,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8298,7 +8294,7 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8318,12 +8314,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8331,24 +8327,24 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>沪A08953A</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8361,34 +8357,34 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±12分钟</t>
+          <t>16:22采样：该车到重点站新川路华东路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8402,47 +8398,880 @@
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr">
         <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
           <t>16:20</t>
         </is>
       </c>
-      <c r="V67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>69分钟</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>16:22采样：该车到重点站金杨路金桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W67" s="2" t="inlineStr">
+      <c r="W68" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X67" s="2" t="inlineStr">
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y67" s="2" t="inlineStr">
+      <c r="Y69" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z67" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>72.8</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>74.3</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
         <is>
           <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,17 +3326,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,22 +3679,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,22 +3794,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,22 +4385,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,17 +4504,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,17 +4857,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,22 +5095,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,22 +5214,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5690,17 +5690,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,22 +5928,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6047,22 +6047,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6166,22 +6166,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6523,22 +6523,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6642,17 +6642,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6761,22 +6761,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6880,22 +6880,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,17 +6999,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,22 +7237,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7475,22 +7475,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7647,24 +7647,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7713,22 +7713,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -7778,10 +7778,14 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:22采样，终点ETA 17分钟</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -7789,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7813,12 +7817,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7838,7 +7842,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7876,29 +7880,29 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>16:22采样：该车到重点站唐陆公路龙东大道 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±8分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7908,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7932,12 +7936,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7947,17 +7951,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7995,29 +7999,29 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>16:22采样：该车到重点站唐陆公路川桥路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±8分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8027,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8051,12 +8055,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8076,12 +8080,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8114,29 +8118,29 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>16:22采样：该车到重点站德川路华夏东路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±13分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8146,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8170,12 +8174,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8185,22 +8189,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8238,26 +8242,22 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>16:22采样：该车到重点站唐陆公路川桥路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 14分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8304,22 +8304,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8352,29 +8352,29 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>16:22采样：该车到重点站新川路华东路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8423,22 +8423,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8471,29 +8471,29 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>16:22采样：该车到重点站金杨路金桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8595,24 +8595,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
+          <t>同车下一次反向发车18:01，减去该车自身同类时段历史终点停站中位数19分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8661,22 +8661,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8714,19 +8714,19 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±5分钟</t>
+          <t>17:21采样：该车到重点站唐陆公路锦绣东路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8833,19 +8833,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±5分钟</t>
+          <t>17:21采样：该车到重点站华夏三路新德西路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数17分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8909,12 +8909,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8957,14 +8957,14 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>17:11采样：该车到重点站唐陆公路南曹路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9041,22 +9041,22 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9083,22 +9083,22 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±6分钟</t>
+          <t>17:11采样：该车到重点站唐陆公路南曹路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9147,12 +9147,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9160,7 +9160,7 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -9190,34 +9190,34 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±14分钟</t>
+          <t>17:21采样：该车到重点站唐陆公路春雅路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9231,47 +9231,999 @@
       <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="V74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W74" s="2" t="inlineStr">
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>17:21采样：该车到重点站长岛路台儿庄路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X74" s="2" t="inlineStr">
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y74" s="2" t="inlineStr">
+      <c r="Y77" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z74" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>79.2</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
         <is>
           <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数96分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>19:42</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,17 +2374,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,22 +3909,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,17 +4028,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,22 +4385,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,17 +4504,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,17 +4623,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5333,17 +5333,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,22 +5452,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5690,17 +5690,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5809,17 +5809,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,22 +5928,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6285,22 +6285,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6404,22 +6404,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6523,22 +6523,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6642,17 +6642,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6771,12 +6771,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,22 +7118,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7475,22 +7475,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,17 +7594,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7832,17 +7832,17 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8189,22 +8189,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8237,27 +8237,31 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 14分钟</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8265,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8289,12 +8293,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8314,12 +8318,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8433,12 +8437,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8557,7 +8561,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8590,29 +8594,29 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车18:01，减去该车自身同类时段历史终点停站中位数19分钟，约±14分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8622,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8646,12 +8650,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8671,12 +8675,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8709,24 +8713,24 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站唐陆公路锦绣东路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -8741,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8765,12 +8769,12 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8780,22 +8784,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8832,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8838,19 +8842,19 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站华夏三路新德西路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数17分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8860,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8884,12 +8888,12 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8899,17 +8903,17 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8952,26 +8956,22 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>17:11采样：该车到重点站唐陆公路南曹路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:02采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9018,22 +9018,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9066,29 +9066,29 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>17:11采样：该车到重点站唐陆公路南曹路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9137,22 +9137,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -9185,29 +9185,29 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站唐陆公路春雅路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9256,17 +9256,17 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9304,29 +9304,29 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9375,17 +9375,17 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9423,29 +9423,29 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站长岛路台儿庄路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±13分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9547,24 +9547,24 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±14分钟</t>
+          <t>18:21采样：该车到重点站新川路华东路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9598,12 +9598,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9613,22 +9613,22 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9666,19 +9666,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>18:02采样：该车到重点站唐陆公路唐镇路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9742,12 +9742,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9785,24 +9785,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±8分钟</t>
+          <t>18:21采样：该车到重点站唐陆公路龙东大道 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9836,12 +9836,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9861,12 +9861,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9904,24 +9904,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±6分钟</t>
+          <t>18:21采样：该车到重点站唐陆公路龙东大道 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -10035,12 +10035,12 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数96分钟估算，约±8分钟</t>
+          <t>18:21采样：该车到重点站唐陆公路龙东大道 ETA 34分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10112,24 +10112,24 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10142,24 +10142,24 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+          <t>18:21采样：该车到重点站博兴路东陆路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10193,37 +10193,870 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>18:21采样：该车到重点站新川路华东路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X82" s="2" t="inlineStr">
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>82.1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y82" s="2" t="inlineStr">
+      <c r="Y84" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z82" s="2" t="inlineStr">
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
+      <c r="AA85" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
-        <is>
-          <t>82.4</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr">
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>98分钟</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数98分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
         <is>
           <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>82.6</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,22 +3679,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,22 +3794,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,22 +4028,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,22 +4857,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,22 +5095,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,22 +5214,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5333,22 +5333,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6166,22 +6166,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6761,22 +6761,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,22 +6999,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,22 +7237,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7485,12 +7485,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,22 +7594,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7713,22 +7713,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7951,22 +7951,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8308,22 +8308,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8427,22 +8427,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8903,22 +8903,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9147,12 +9147,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9542,29 +9542,29 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站新川路华东路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9598,12 +9598,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9666,26 +9666,22 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>18:02采样：该车到重点站唐陆公路唐镇路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:41采样，终点ETA 18分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9693,7 +9689,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9722,7 +9718,7 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9732,22 +9728,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -9780,29 +9776,29 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>106分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站唐陆公路龙东大道 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9812,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9836,12 +9832,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9851,22 +9847,22 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9899,29 +9895,29 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站唐陆公路龙东大道 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9931,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9955,12 +9951,12 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9970,22 +9966,22 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10018,29 +10014,29 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站唐陆公路龙东大道 ETA 34分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10050,7 +10046,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10074,12 +10070,12 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10099,12 +10095,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10142,26 +10138,22 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站博兴路东陆路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±14分钟</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 16分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10169,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10193,12 +10185,12 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10218,12 +10210,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10256,29 +10248,29 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站新川路华东路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10288,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10312,12 +10304,12 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10327,22 +10319,22 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10380,19 +10372,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+          <t>19:21采样：该车到重点站新川路川沙路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数6分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -10407,7 +10399,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10436,7 +10428,7 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10456,7 +10448,7 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10499,26 +10491,22 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 33分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10526,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10550,12 +10538,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10565,22 +10553,22 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10618,24 +10606,24 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数98分钟估算，约±10分钟</t>
+          <t>19:21采样：该车到重点站唐陆公路春雅路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10645,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10669,12 +10657,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10694,12 +10682,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10737,24 +10725,24 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±7分钟</t>
+          <t>19:21采样：该车到重点站东陆路金海路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10764,7 +10752,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10793,7 +10781,7 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10813,7 +10801,7 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10856,19 +10844,19 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±5分钟</t>
+          <t>19:21采样：该车到重点站新德西路德翔路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -10883,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10912,7 +10900,7 @@
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10932,12 +10920,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10945,24 +10933,24 @@
       <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10975,34 +10963,34 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+          <t>19:21采样：该车到重点站东陆路金海路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11016,47 +11004,642 @@
       <c r="T89" s="2" t="inlineStr"/>
       <c r="U89" s="2" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W89" s="2" t="inlineStr">
+      <c r="W90" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X89" s="2" t="inlineStr">
+      <c r="X90" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y89" s="2" t="inlineStr">
+      <c r="Y90" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z89" s="2" t="inlineStr">
+      <c r="Z90" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
+      <c r="AA90" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AB89" s="2" t="inlineStr">
-        <is>
-          <t>82.6</t>
-        </is>
-      </c>
-      <c r="AC89" s="2" t="inlineStr">
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>82.1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
         <is>
           <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>21:02</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,22 +3794,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,22 +4623,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,22 +5214,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5809,22 +5809,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,22 +5928,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6166,22 +6166,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7832,22 +7832,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8189,22 +8189,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8427,22 +8427,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9256,22 +9256,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9613,22 +9613,22 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9847,22 +9847,22 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10133,12 +10133,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -10150,10 +10150,14 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 16分钟</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10161,7 +10165,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10185,12 +10189,12 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10253,24 +10257,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10280,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10329,12 +10333,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10367,29 +10371,29 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站新川路川沙路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数6分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10399,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10423,12 +10427,12 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10448,12 +10452,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10486,27 +10490,31 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 33分钟</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10514,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10538,12 +10546,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10568,7 +10576,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10601,29 +10609,29 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站唐陆公路春雅路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10633,7 +10641,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10657,12 +10665,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10682,7 +10690,7 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10725,26 +10733,22 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站东陆路金海路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:01采样，终点ETA 12分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -10752,7 +10756,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10781,7 +10785,7 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10801,7 +10805,7 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10839,29 +10843,29 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站新德西路德翔路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10871,7 +10875,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10895,12 +10899,12 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10910,22 +10914,22 @@
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10958,29 +10962,29 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站东陆路金海路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10990,7 +10994,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11014,12 +11018,12 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11039,7 +11043,7 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11077,29 +11081,29 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11109,7 +11113,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11133,12 +11137,12 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11158,12 +11162,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11196,29 +11200,29 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11228,7 +11232,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11252,12 +11256,12 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
@@ -11267,22 +11271,22 @@
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11320,24 +11324,24 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±13分钟</t>
+          <t>20:21采样：该车到重点站唐陆公路川桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11347,7 +11351,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11376,7 +11380,7 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11396,12 +11400,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11439,26 +11443,22 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 40分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11505,22 +11505,22 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -11558,19 +11558,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±11分钟</t>
+          <t>20:21采样：该车到重点站博兴路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11614,32 +11614,389 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>70分钟</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y94" s="2" t="inlineStr">
+      <c r="Y95" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z94" s="2" t="inlineStr">
+      <c r="Z95" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AA94" s="2" t="inlineStr">
+      <c r="AA95" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AB94" s="2" t="inlineStr">
-        <is>
-          <t>75.5</t>
-        </is>
-      </c>
-      <c r="AC94" s="2" t="inlineStr">
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>74.4</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
         <is>
           <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-182路.xlsx
+++ b/data/export/2026-09-22-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9623,12 +9623,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10967,12 +10967,12 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11086,24 +11086,24 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:48</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11319,29 +11319,29 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站唐陆公路川桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±12分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11375,12 +11375,12 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11438,12 +11438,12 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -11455,10 +11455,14 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 40分钟</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11466,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11490,12 +11494,12 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11515,7 +11519,7 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11553,29 +11557,29 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站博兴路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -11585,7 +11589,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11609,12 +11613,12 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
@@ -11634,7 +11638,7 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11672,29 +11676,29 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11704,7 +11708,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11728,12 +11732,12 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
@@ -11753,7 +11757,7 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11796,26 +11800,22 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:22采样，终点ETA 42分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11847,12 +11847,12 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11872,12 +11872,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11920,19 +11920,19 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
+          <t>21:22采样：该车到重点站长岛路台儿庄路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
